--- a/public/upload_template.xlsx
+++ b/public/upload_template.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveycstech-my.sharepoint.com/personal/csmith_ytech_edu/Documents/fastprojects/QuizBank/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\quizbank\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F943C92E-4ACE-4DB5-9ECB-C5E2CA053A4B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F6D2E1-7339-4C39-B6D3-0D0AF2707A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375" xr2:uid="{55207F7B-737E-4D56-8AF8-6FECFF75A869}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{55207F7B-737E-4D56-8AF8-6FECFF75A869}"/>
   </bookViews>
   <sheets>
     <sheet name="Course" sheetId="1" r:id="rId1"/>
     <sheet name="Vocabulary" sheetId="2" r:id="rId2"/>
+    <sheet name="Questions" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
-  <si>
-    <t>Course ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Unit ID</t>
   </si>
@@ -37,9 +35,6 @@
     <t>Unit Name</t>
   </si>
   <si>
-    <t>Course Name</t>
-  </si>
-  <si>
     <t>Task ID</t>
   </si>
   <si>
@@ -53,6 +48,27 @@
   </si>
   <si>
     <t>Definition</t>
+  </si>
+  <si>
+    <t>Task Description</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Correct Answer</t>
+  </si>
+  <si>
+    <t>Answer 1</t>
+  </si>
+  <si>
+    <t>Answer 2</t>
+  </si>
+  <si>
+    <t>Answer 3</t>
+  </si>
+  <si>
+    <t>Answer 4</t>
   </si>
 </sst>
 </file>
@@ -108,9 +124,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -148,7 +164,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -254,7 +270,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -396,7 +412,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -404,38 +420,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68191B63-612F-406B-8890-CF003BA9B642}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -453,13 +465,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -467,7 +479,49 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B92C219-2EB4-4824-94BA-8A457631DE1C}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA223F759147049B9D8A25DED07DD24" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd9bc9ef329b974a7c970eeaee05a8c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="cc9255bc-4d99-4f42-bba5-857cbcc6e725" xmlns:ns4="fc2bff61-6a31-4c51-9f32-b9bba46405e5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eb5337197d31bfe391c0ed738c4a9196" ns3:_="" ns4:_="">
     <xsd:import namespace="cc9255bc-4d99-4f42-bba5-857cbcc6e725"/>
@@ -720,15 +774,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -738,6 +783,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2C8398A-20B8-41BE-BD7C-B4B792F01B93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1472A8AC-468C-4273-8F76-00D42060E0C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -756,14 +809,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2C8398A-20B8-41BE-BD7C-B4B792F01B93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1429352D-1B89-4217-9189-D83CF7174217}">
   <ds:schemaRefs>

--- a/public/upload_template.xlsx
+++ b/public/upload_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\quizbank\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csmith.PROG\Documents\GitHub\quizbank\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F6D2E1-7339-4C39-B6D3-0D0AF2707A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6063AE-76A1-4DD9-B53F-39393A8C3191}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{55207F7B-737E-4D56-8AF8-6FECFF75A869}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Unit ID</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Answer 4</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
@@ -124,9 +127,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +167,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -270,7 +273,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -412,7 +415,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -481,10 +484,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B92C219-2EB4-4824-94BA-8A457631DE1C}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -492,18 +495,21 @@
         <v>8</v>
       </c>
       <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -513,12 +519,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="cc9255bc-4d99-4f42-bba5-857cbcc6e725" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -775,17 +780,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="cc9255bc-4d99-4f42-bba5-857cbcc6e725" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2C8398A-20B8-41BE-BD7C-B4B792F01B93}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1429352D-1B89-4217-9189-D83CF7174217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="cc9255bc-4d99-4f42-bba5-857cbcc6e725"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fc2bff61-6a31-4c51-9f32-b9bba46405e5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -810,18 +825,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1429352D-1B89-4217-9189-D83CF7174217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2C8398A-20B8-41BE-BD7C-B4B792F01B93}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="cc9255bc-4d99-4f42-bba5-857cbcc6e725"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fc2bff61-6a31-4c51-9f32-b9bba46405e5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>